--- a/Ozrit HR data/ozrit/Admin/Parking Slot/Parking Slots_.xlsx
+++ b/Ozrit HR data/ozrit/Admin/Parking Slot/Parking Slots_.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\Admin\Parking Slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC658AD-BAA4-4A46-9B57-89274F80C4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t xml:space="preserve">Employee Details </t>
   </si>
@@ -31,12 +40,6 @@
     <t>Parking Slot</t>
   </si>
   <si>
-    <t>Asif</t>
-  </si>
-  <si>
-    <t>AP28 DK 4118</t>
-  </si>
-  <si>
     <t>B3-28</t>
   </si>
   <si>
@@ -85,21 +88,12 @@
     <t>B3-27</t>
   </si>
   <si>
-    <t>Srikanth</t>
-  </si>
-  <si>
-    <t>AP29AB1603</t>
-  </si>
-  <si>
     <t>B3-40</t>
   </si>
   <si>
     <t>Manikanta</t>
   </si>
   <si>
-    <t>AP35AA6215</t>
-  </si>
-  <si>
     <t>B3-75</t>
   </si>
   <si>
@@ -121,12 +115,6 @@
     <t>B3-77</t>
   </si>
   <si>
-    <t>Chary</t>
-  </si>
-  <si>
-    <t>Ap39NL2092</t>
-  </si>
-  <si>
     <t>B3-78</t>
   </si>
   <si>
@@ -155,93 +143,168 @@
   </si>
   <si>
     <t>B3-137</t>
+  </si>
+  <si>
+    <t>Yuva Kiran</t>
+  </si>
+  <si>
+    <t>B3(118)       </t>
+  </si>
+  <si>
+    <t>TS35D0606</t>
+  </si>
+  <si>
+    <t>Kiran</t>
+  </si>
+  <si>
+    <t>B3(119)</t>
+  </si>
+  <si>
+    <t>TS07GA9638</t>
+  </si>
+  <si>
+    <t>Raghu</t>
+  </si>
+  <si>
+    <t>B3(120)</t>
+  </si>
+  <si>
+    <t>TS07GA6903    </t>
+  </si>
+  <si>
+    <t>Chetan</t>
+  </si>
+  <si>
+    <t>B3(126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sai kumar laravel </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF2C363A"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2C363A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="5">
-    <border/>
+  <borders count="7">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -251,52 +314,148 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -486,287 +645,398 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A2:I28"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="12.6328125" style="19"/>
+  </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+    </row>
+    <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="C4" s="7" t="s">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4">
+        <v>8</v>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="B5" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="B6" s="7">
-        <v>16.0</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4">
+        <v>24</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="B7" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B11" s="4">
+        <v>49</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4">
+        <v>32</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4">
+        <v>46</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4">
+        <v>12</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>12</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <v>13</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
         <v>14</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="B17" s="13">
+        <v>50</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
         <v>15</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
         <v>16</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="B19" s="15"/>
+      <c r="C19" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
         <v>17</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B8" s="7">
-        <v>24.0</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B20" s="15"/>
+      <c r="C20" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
         <v>18</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="B9" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="B10" s="7">
-        <v>31.0</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="B11" s="7">
-        <v>49.0</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="B12" s="7">
-        <v>32.0</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="B13" s="7">
-        <v>46.0</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="B14" s="7">
-        <v>12.0</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6">
-        <v>14.0</v>
-      </c>
-      <c r="B17" s="7">
-        <v>50.0</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>47</v>
-      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>